--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/112-114年臺東縣平假日分析.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/112-114年臺東縣平假日分析.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">景點</t>
   </si>
@@ -38,12 +38,18 @@
     <t xml:space="preserve">99.14%</t>
   </si>
   <si>
-    <t xml:space="preserve">卑南初鹿地區</t>
+    <t xml:space="preserve">初鹿地區</t>
   </si>
   <si>
     <t xml:space="preserve">244.21%</t>
   </si>
   <si>
+    <t xml:space="preserve">加路蘭遊憩區</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">富岡漁港及小野柳</t>
   </si>
   <si>
@@ -89,7 +95,7 @@
     <t xml:space="preserve">總計</t>
   </si>
   <si>
-    <t xml:space="preserve">103.17%</t>
+    <t xml:space="preserve">103.21%</t>
   </si>
 </sst>
 </file>
@@ -483,16 +489,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>57803</v>
+        <v>8563</v>
       </c>
       <c r="C4" t="n">
-        <v>24744</v>
+        <v>3214</v>
       </c>
       <c r="D4" t="n">
-        <v>73.8224776500639</v>
+        <v>10.9361430395913</v>
       </c>
       <c r="E4" t="n">
-        <v>79.0543130990415</v>
+        <v>10.2683706070288</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -503,16 +509,16 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7624</v>
+        <v>57803</v>
       </c>
       <c r="C5" t="n">
-        <v>2751</v>
+        <v>24744</v>
       </c>
       <c r="D5" t="n">
-        <v>9.73690932311622</v>
+        <v>73.8224776500639</v>
       </c>
       <c r="E5" t="n">
-        <v>8.78913738019169</v>
+        <v>79.0543130990415</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -523,16 +529,16 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
-        <v>3454</v>
+        <v>7624</v>
       </c>
       <c r="C6" t="n">
-        <v>1349</v>
+        <v>2751</v>
       </c>
       <c r="D6" t="n">
-        <v>4.41123882503193</v>
+        <v>9.73690932311622</v>
       </c>
       <c r="E6" t="n">
-        <v>4.30990415335463</v>
+        <v>8.78913738019169</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -543,16 +549,16 @@
         <v>16</v>
       </c>
       <c r="B7" t="n">
-        <v>210184</v>
+        <v>3454</v>
       </c>
       <c r="C7" t="n">
-        <v>89929</v>
+        <v>1349</v>
       </c>
       <c r="D7" t="n">
-        <v>268.434227330779</v>
+        <v>4.41123882503193</v>
       </c>
       <c r="E7" t="n">
-        <v>287.313099041534</v>
+        <v>4.30990415335463</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -563,16 +569,16 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>416285</v>
+        <v>210184</v>
       </c>
       <c r="C8" t="n">
-        <v>161018</v>
+        <v>89929</v>
       </c>
       <c r="D8" t="n">
-        <v>531.653895274585</v>
+        <v>268.434227330779</v>
       </c>
       <c r="E8" t="n">
-        <v>514.434504792332</v>
+        <v>287.313099041534</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
@@ -583,16 +589,16 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>45143</v>
+        <v>416285</v>
       </c>
       <c r="C9" t="n">
-        <v>13601</v>
+        <v>161018</v>
       </c>
       <c r="D9" t="n">
-        <v>57.6538952745849</v>
+        <v>531.653895274585</v>
       </c>
       <c r="E9" t="n">
-        <v>43.4536741214058</v>
+        <v>514.434504792332</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -603,16 +609,16 @@
         <v>22</v>
       </c>
       <c r="B10" t="n">
-        <v>1278</v>
+        <v>45143</v>
       </c>
       <c r="C10" t="n">
-        <v>419</v>
+        <v>13601</v>
       </c>
       <c r="D10" t="n">
-        <v>1.63218390804598</v>
+        <v>57.6538952745849</v>
       </c>
       <c r="E10" t="n">
-        <v>1.33865814696486</v>
+        <v>43.4536741214058</v>
       </c>
       <c r="F10" t="s">
         <v>23</v>
@@ -623,19 +629,39 @@
         <v>24</v>
       </c>
       <c r="B11" t="n">
-        <v>784568</v>
+        <v>1278</v>
       </c>
       <c r="C11" t="n">
-        <v>303976</v>
+        <v>419</v>
       </c>
       <c r="D11" t="n">
-        <v>1002.00255427842</v>
+        <v>1.63218390804598</v>
       </c>
       <c r="E11" t="n">
-        <v>971.169329073482</v>
+        <v>1.33865814696486</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="n">
+        <v>793131</v>
+      </c>
+      <c r="C12" t="n">
+        <v>307190</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1012.93869731801</v>
+      </c>
+      <c r="E12" t="n">
+        <v>981.437699680511</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
